--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128856597</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128852128</v>
       </c>
       <c r="B3" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128848051</v>
       </c>
       <c r="B4" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128847827</v>
       </c>
       <c r="B6" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128847563</v>
       </c>
       <c r="B7" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,6 +1263,478 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128885108</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98625</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mossen NO 1390 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>568037</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6506715</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128884959</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98625</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mossen NO 1420 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>568015</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6506779</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128885003</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98625</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mossen NO 1440 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>568021</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6506793</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128885129</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105688</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mossen NO 1390 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>568037</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6506715</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128856597</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128852128</v>
       </c>
       <c r="B3" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128848051</v>
       </c>
       <c r="B4" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128847827</v>
       </c>
       <c r="B6" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128847563</v>
       </c>
       <c r="B7" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,45 +1266,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128885108</v>
+        <v>128885129</v>
       </c>
       <c r="B8" t="n">
-        <v>98625</v>
+        <v>105695</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1381,10 +1385,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128884959</v>
+        <v>128885108</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1411,7 +1415,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1421,24 +1425,24 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mossen NO 1420 m, Ög</t>
+          <t>Mossen NO 1390 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568015</v>
+        <v>568037</v>
       </c>
       <c r="R9" t="n">
-        <v>6506779</v>
+        <v>6506715</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1500,10 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128885003</v>
+        <v>128884959</v>
       </c>
       <c r="B10" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1530,7 +1534,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1547,17 +1551,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mossen NO 1440 m, Ög</t>
+          <t>Mossen NO 1420 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568021</v>
+        <v>568015</v>
       </c>
       <c r="R10" t="n">
-        <v>6506793</v>
+        <v>6506779</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1587,6 +1591,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>I närområdet är totalt 149 knärotsskott observerade.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1619,42 +1628,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128885129</v>
+        <v>128885003</v>
       </c>
       <c r="B11" t="n">
-        <v>105688</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1666,14 +1675,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mossen NO 1390 m, Ög</t>
+          <t>Mossen NO 1440 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568037</v>
+        <v>568021</v>
       </c>
       <c r="R11" t="n">
-        <v>6506715</v>
+        <v>6506793</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,6 +1715,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>I närområdet är totalt 149 knärotsskott observerade.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1750,6 +1750,1239 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128912582</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Råsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>568004</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6506793</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128920148</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Råsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>568107</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6506598</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128912308</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Råsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>568116</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6506669</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128912870</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Råsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>567991</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6506744</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128912730</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Råsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>567992</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6506757</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128912804</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79739</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Råsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>567994</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6506732</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128912556</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Råsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>568009</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6506870</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128912437</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92136</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Råsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>568125</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6506664</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128912854</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Råsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>567998</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6506728</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128912171</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78786</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>353</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Råsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>568118</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6506590</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128920214</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Råsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>568014</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6506845</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128912308</v>
+        <v>128912730</v>
       </c>
       <c r="B14" t="n">
-        <v>92832</v>
+        <v>79739</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,21 +1991,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>568116</v>
+        <v>567992</v>
       </c>
       <c r="R14" t="n">
-        <v>6506669</v>
+        <v>6506757</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,7 +2091,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128912870</v>
+        <v>128912308</v>
       </c>
       <c r="B15" t="n">
         <v>92832</v>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567991</v>
+        <v>568116</v>
       </c>
       <c r="R15" t="n">
-        <v>6506744</v>
+        <v>6506669</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912730</v>
+        <v>128912870</v>
       </c>
       <c r="B16" t="n">
-        <v>79739</v>
+        <v>92832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567992</v>
+        <v>567991</v>
       </c>
       <c r="R16" t="n">
-        <v>6506757</v>
+        <v>6506744</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128856597</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128852128</v>
       </c>
       <c r="B3" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128848051</v>
       </c>
       <c r="B4" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128847827</v>
       </c>
       <c r="B6" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128847563</v>
       </c>
       <c r="B7" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128885129</v>
       </c>
       <c r="B8" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>128885108</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128884959</v>
       </c>
       <c r="B10" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>128885003</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128912582</v>
       </c>
       <c r="B12" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>128912730</v>
       </c>
       <c r="B14" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
         <v>128912308</v>
       </c>
       <c r="B15" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>128912870</v>
       </c>
       <c r="B16" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2316,7 +2316,7 @@
         <v>128912804</v>
       </c>
       <c r="B17" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>128912556</v>
       </c>
       <c r="B18" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>128912437</v>
       </c>
       <c r="B19" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>128912854</v>
       </c>
       <c r="B20" t="n">
-        <v>91923</v>
+        <v>91927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2760,7 +2760,7 @@
         <v>128912171</v>
       </c>
       <c r="B21" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128912730</v>
+        <v>128912308</v>
       </c>
       <c r="B14" t="n">
-        <v>79743</v>
+        <v>92836</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,21 +1991,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567992</v>
+        <v>568116</v>
       </c>
       <c r="R14" t="n">
-        <v>6506757</v>
+        <v>6506669</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,14 +2084,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128912308</v>
+        <v>128912870</v>
       </c>
       <c r="B15" t="n">
         <v>92836</v>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568116</v>
+        <v>567991</v>
       </c>
       <c r="R15" t="n">
-        <v>6506669</v>
+        <v>6506744</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912870</v>
+        <v>128912730</v>
       </c>
       <c r="B16" t="n">
-        <v>92836</v>
+        <v>79743</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567991</v>
+        <v>567992</v>
       </c>
       <c r="R16" t="n">
-        <v>6506744</v>
+        <v>6506757</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2424,32 +2424,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128912556</v>
+        <v>128912437</v>
       </c>
       <c r="B18" t="n">
-        <v>92836</v>
+        <v>92140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,13 +2462,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568009</v>
+        <v>568125</v>
       </c>
       <c r="R18" t="n">
-        <v>6506870</v>
+        <v>6506664</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2535,32 +2535,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128912437</v>
+        <v>128912556</v>
       </c>
       <c r="B19" t="n">
-        <v>92140</v>
+        <v>92836</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568125</v>
+        <v>568009</v>
       </c>
       <c r="R19" t="n">
-        <v>6506664</v>
+        <v>6506870</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -2424,32 +2424,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128912437</v>
+        <v>128912556</v>
       </c>
       <c r="B18" t="n">
-        <v>92140</v>
+        <v>92836</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,13 +2462,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568125</v>
+        <v>568009</v>
       </c>
       <c r="R18" t="n">
-        <v>6506664</v>
+        <v>6506870</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2535,32 +2535,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128912556</v>
+        <v>128912437</v>
       </c>
       <c r="B19" t="n">
-        <v>92836</v>
+        <v>92140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568009</v>
+        <v>568125</v>
       </c>
       <c r="R19" t="n">
-        <v>6506870</v>
+        <v>6506664</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128856597</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128852128</v>
       </c>
       <c r="B3" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128848051</v>
       </c>
       <c r="B4" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128847827</v>
       </c>
       <c r="B6" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128847563</v>
       </c>
       <c r="B7" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128885129</v>
       </c>
       <c r="B8" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>128885108</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128884959</v>
       </c>
       <c r="B10" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>128885003</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128912582</v>
       </c>
       <c r="B12" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128912308</v>
+        <v>128912870</v>
       </c>
       <c r="B14" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>568116</v>
+        <v>567991</v>
       </c>
       <c r="R14" t="n">
-        <v>6506669</v>
+        <v>6506744</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128912870</v>
+        <v>128912730</v>
       </c>
       <c r="B15" t="n">
-        <v>92836</v>
+        <v>79648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567991</v>
+        <v>567992</v>
       </c>
       <c r="R15" t="n">
-        <v>6506744</v>
+        <v>6506757</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2202,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912730</v>
+        <v>128912308</v>
       </c>
       <c r="B16" t="n">
-        <v>79743</v>
+        <v>92841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567992</v>
+        <v>568116</v>
       </c>
       <c r="R16" t="n">
-        <v>6506757</v>
+        <v>6506669</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,7 +2316,7 @@
         <v>128912804</v>
       </c>
       <c r="B17" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,32 +2424,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128912556</v>
+        <v>128912437</v>
       </c>
       <c r="B18" t="n">
-        <v>92836</v>
+        <v>92145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,13 +2462,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568009</v>
+        <v>568125</v>
       </c>
       <c r="R18" t="n">
-        <v>6506870</v>
+        <v>6506664</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2535,32 +2535,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128912437</v>
+        <v>128912556</v>
       </c>
       <c r="B19" t="n">
-        <v>92140</v>
+        <v>92841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568125</v>
+        <v>568009</v>
       </c>
       <c r="R19" t="n">
-        <v>6506664</v>
+        <v>6506870</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,7 +2649,7 @@
         <v>128912854</v>
       </c>
       <c r="B20" t="n">
-        <v>91927</v>
+        <v>91932</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>128912171</v>
       </c>
       <c r="B21" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128912730</v>
+        <v>128912308</v>
       </c>
       <c r="B14" t="n">
-        <v>79653</v>
+        <v>92849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,21 +1991,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567992</v>
+        <v>568116</v>
       </c>
       <c r="R14" t="n">
-        <v>6506757</v>
+        <v>6506669</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,7 +2091,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128912308</v>
+        <v>128912870</v>
       </c>
       <c r="B15" t="n">
         <v>92849</v>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568116</v>
+        <v>567991</v>
       </c>
       <c r="R15" t="n">
-        <v>6506669</v>
+        <v>6506744</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912870</v>
+        <v>128912730</v>
       </c>
       <c r="B16" t="n">
-        <v>92849</v>
+        <v>79653</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567991</v>
+        <v>567992</v>
       </c>
       <c r="R16" t="n">
-        <v>6506744</v>
+        <v>6506757</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128856597</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128852128</v>
       </c>
       <c r="B3" t="n">
-        <v>92153</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128848051</v>
       </c>
       <c r="B4" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128847827</v>
       </c>
       <c r="B6" t="n">
-        <v>92153</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128847563</v>
       </c>
       <c r="B7" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128885129</v>
       </c>
       <c r="B8" t="n">
-        <v>105714</v>
+        <v>105719</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>128885108</v>
       </c>
       <c r="B9" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128884959</v>
       </c>
       <c r="B10" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>128885003</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128912582</v>
       </c>
       <c r="B12" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128912308</v>
+        <v>128912730</v>
       </c>
       <c r="B14" t="n">
-        <v>92849</v>
+        <v>79653</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,21 +1991,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>568116</v>
+        <v>567992</v>
       </c>
       <c r="R14" t="n">
-        <v>6506669</v>
+        <v>6506757</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128912870</v>
+        <v>128912308</v>
       </c>
       <c r="B15" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567991</v>
+        <v>568116</v>
       </c>
       <c r="R15" t="n">
-        <v>6506744</v>
+        <v>6506669</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912730</v>
+        <v>128912870</v>
       </c>
       <c r="B16" t="n">
-        <v>79653</v>
+        <v>92854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567992</v>
+        <v>567991</v>
       </c>
       <c r="R16" t="n">
-        <v>6506757</v>
+        <v>6506744</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2424,32 +2424,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128912437</v>
+        <v>128912556</v>
       </c>
       <c r="B18" t="n">
-        <v>92153</v>
+        <v>92854</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,13 +2462,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568125</v>
+        <v>568009</v>
       </c>
       <c r="R18" t="n">
-        <v>6506664</v>
+        <v>6506870</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2535,32 +2535,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128912556</v>
+        <v>128912437</v>
       </c>
       <c r="B19" t="n">
-        <v>92849</v>
+        <v>92158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568009</v>
+        <v>568125</v>
       </c>
       <c r="R19" t="n">
-        <v>6506870</v>
+        <v>6506664</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,7 +2649,7 @@
         <v>128912854</v>
       </c>
       <c r="B20" t="n">
-        <v>91940</v>
+        <v>91943</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>129044110</v>
       </c>
       <c r="B23" t="n">
-        <v>92153</v>
+        <v>92158</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>129044023</v>
       </c>
       <c r="B24" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>129043539</v>
       </c>
       <c r="B25" t="n">
-        <v>92153</v>
+        <v>92158</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>129043245</v>
       </c>
       <c r="B26" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128856597</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128852128</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92161</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128848051</v>
       </c>
       <c r="B4" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128847827</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92161</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128847563</v>
       </c>
       <c r="B7" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128885129</v>
       </c>
       <c r="B8" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>128885108</v>
       </c>
       <c r="B9" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128884959</v>
       </c>
       <c r="B10" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>128885003</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128912582</v>
       </c>
       <c r="B12" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128912730</v>
+        <v>128912308</v>
       </c>
       <c r="B14" t="n">
-        <v>79653</v>
+        <v>92857</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,21 +1991,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567992</v>
+        <v>568116</v>
       </c>
       <c r="R14" t="n">
-        <v>6506757</v>
+        <v>6506669</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128912308</v>
+        <v>128912870</v>
       </c>
       <c r="B15" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568116</v>
+        <v>567991</v>
       </c>
       <c r="R15" t="n">
-        <v>6506669</v>
+        <v>6506744</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912870</v>
+        <v>128912730</v>
       </c>
       <c r="B16" t="n">
-        <v>92854</v>
+        <v>79654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567991</v>
+        <v>567992</v>
       </c>
       <c r="R16" t="n">
-        <v>6506744</v>
+        <v>6506757</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,7 +2316,7 @@
         <v>128912804</v>
       </c>
       <c r="B17" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>128912556</v>
       </c>
       <c r="B18" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>128912437</v>
       </c>
       <c r="B19" t="n">
-        <v>92158</v>
+        <v>92161</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>128912854</v>
       </c>
       <c r="B20" t="n">
-        <v>91943</v>
+        <v>91946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>128912171</v>
       </c>
       <c r="B21" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>129044110</v>
       </c>
       <c r="B23" t="n">
-        <v>92158</v>
+        <v>92161</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>129044023</v>
       </c>
       <c r="B24" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>129043539</v>
       </c>
       <c r="B25" t="n">
-        <v>92158</v>
+        <v>92161</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>129043245</v>
       </c>
       <c r="B26" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128912308</v>
+        <v>128912730</v>
       </c>
       <c r="B14" t="n">
-        <v>92857</v>
+        <v>79654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,21 +1991,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>568116</v>
+        <v>567992</v>
       </c>
       <c r="R14" t="n">
-        <v>6506669</v>
+        <v>6506757</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,7 +2091,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128912870</v>
+        <v>128912308</v>
       </c>
       <c r="B15" t="n">
         <v>92857</v>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567991</v>
+        <v>568116</v>
       </c>
       <c r="R15" t="n">
-        <v>6506744</v>
+        <v>6506669</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912730</v>
+        <v>128912870</v>
       </c>
       <c r="B16" t="n">
-        <v>79654</v>
+        <v>92857</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567992</v>
+        <v>567991</v>
       </c>
       <c r="R16" t="n">
-        <v>6506757</v>
+        <v>6506744</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2424,32 +2424,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128912556</v>
+        <v>128912437</v>
       </c>
       <c r="B18" t="n">
-        <v>92857</v>
+        <v>92161</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,13 +2462,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568009</v>
+        <v>568125</v>
       </c>
       <c r="R18" t="n">
-        <v>6506870</v>
+        <v>6506664</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2535,32 +2535,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128912437</v>
+        <v>128912556</v>
       </c>
       <c r="B19" t="n">
-        <v>92161</v>
+        <v>92857</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568125</v>
+        <v>568009</v>
       </c>
       <c r="R19" t="n">
-        <v>6506664</v>
+        <v>6506870</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -2091,7 +2091,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128912308</v>
+        <v>128912870</v>
       </c>
       <c r="B15" t="n">
         <v>92857</v>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568116</v>
+        <v>567991</v>
       </c>
       <c r="R15" t="n">
-        <v>6506669</v>
+        <v>6506744</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,7 +2202,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912870</v>
+        <v>128912308</v>
       </c>
       <c r="B16" t="n">
         <v>92857</v>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567991</v>
+        <v>568116</v>
       </c>
       <c r="R16" t="n">
-        <v>6506744</v>
+        <v>6506669</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2424,32 +2424,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128912437</v>
+        <v>128912556</v>
       </c>
       <c r="B18" t="n">
-        <v>92161</v>
+        <v>92857</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,13 +2462,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568125</v>
+        <v>568009</v>
       </c>
       <c r="R18" t="n">
-        <v>6506664</v>
+        <v>6506870</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2535,32 +2535,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128912556</v>
+        <v>128912437</v>
       </c>
       <c r="B19" t="n">
-        <v>92857</v>
+        <v>92161</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568009</v>
+        <v>568125</v>
       </c>
       <c r="R19" t="n">
-        <v>6506870</v>
+        <v>6506664</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128856597</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128852128</v>
       </c>
       <c r="B3" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128848051</v>
       </c>
       <c r="B4" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128847827</v>
       </c>
       <c r="B6" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128847563</v>
       </c>
       <c r="B7" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128885129</v>
       </c>
       <c r="B8" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>128885108</v>
       </c>
       <c r="B9" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128884959</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>128885003</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128912582</v>
       </c>
       <c r="B12" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>128912730</v>
       </c>
       <c r="B14" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128912870</v>
+        <v>128912308</v>
       </c>
       <c r="B15" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567991</v>
+        <v>568116</v>
       </c>
       <c r="R15" t="n">
-        <v>6506744</v>
+        <v>6506669</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912308</v>
+        <v>128912870</v>
       </c>
       <c r="B16" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>568116</v>
+        <v>567991</v>
       </c>
       <c r="R16" t="n">
-        <v>6506669</v>
+        <v>6506744</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,7 +2316,7 @@
         <v>128912804</v>
       </c>
       <c r="B17" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>128912556</v>
       </c>
       <c r="B18" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>128912437</v>
       </c>
       <c r="B19" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
         <v>128912854</v>
       </c>
       <c r="B20" t="n">
-        <v>91946</v>
+        <v>91953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>128912171</v>
       </c>
       <c r="B21" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>129044110</v>
       </c>
       <c r="B23" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>129044023</v>
       </c>
       <c r="B24" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>129043539</v>
       </c>
       <c r="B25" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>129043245</v>
       </c>
       <c r="B26" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -2091,7 +2091,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128912308</v>
+        <v>128912870</v>
       </c>
       <c r="B15" t="n">
         <v>92864</v>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568116</v>
+        <v>567991</v>
       </c>
       <c r="R15" t="n">
-        <v>6506669</v>
+        <v>6506744</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,7 +2202,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912870</v>
+        <v>128912308</v>
       </c>
       <c r="B16" t="n">
         <v>92864</v>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567991</v>
+        <v>568116</v>
       </c>
       <c r="R16" t="n">
-        <v>6506744</v>
+        <v>6506669</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128856597</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128852128</v>
       </c>
       <c r="B3" t="n">
-        <v>92168</v>
+        <v>92175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128848051</v>
       </c>
       <c r="B4" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128847827</v>
       </c>
       <c r="B6" t="n">
-        <v>92168</v>
+        <v>92175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128847563</v>
       </c>
       <c r="B7" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128885129</v>
       </c>
       <c r="B8" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>128885108</v>
       </c>
       <c r="B9" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128884959</v>
       </c>
       <c r="B10" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>128885003</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128912582</v>
       </c>
       <c r="B12" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128912730</v>
+        <v>128912308</v>
       </c>
       <c r="B14" t="n">
-        <v>79658</v>
+        <v>92871</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,21 +1991,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567992</v>
+        <v>568116</v>
       </c>
       <c r="R14" t="n">
-        <v>6506757</v>
+        <v>6506669</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2094,7 +2094,7 @@
         <v>128912870</v>
       </c>
       <c r="B15" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912308</v>
+        <v>128912730</v>
       </c>
       <c r="B16" t="n">
-        <v>92864</v>
+        <v>79658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>568116</v>
+        <v>567992</v>
       </c>
       <c r="R16" t="n">
-        <v>6506669</v>
+        <v>6506757</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2427,7 +2427,7 @@
         <v>128912556</v>
       </c>
       <c r="B18" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>128912437</v>
       </c>
       <c r="B19" t="n">
-        <v>92168</v>
+        <v>92175</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
         <v>128912854</v>
       </c>
       <c r="B20" t="n">
-        <v>91953</v>
+        <v>91960</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>129044110</v>
       </c>
       <c r="B23" t="n">
-        <v>92168</v>
+        <v>92175</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>129044023</v>
       </c>
       <c r="B24" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>129043539</v>
       </c>
       <c r="B25" t="n">
-        <v>92168</v>
+        <v>92175</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>129043245</v>
       </c>
       <c r="B26" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128856597</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128852128</v>
       </c>
       <c r="B3" t="n">
-        <v>92175</v>
+        <v>92177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128848051</v>
       </c>
       <c r="B4" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128847827</v>
       </c>
       <c r="B6" t="n">
-        <v>92175</v>
+        <v>92177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128847563</v>
       </c>
       <c r="B7" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128885129</v>
       </c>
       <c r="B8" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>128885108</v>
       </c>
       <c r="B9" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128884959</v>
       </c>
       <c r="B10" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>128885003</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128912582</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128912308</v>
+        <v>128912730</v>
       </c>
       <c r="B14" t="n">
-        <v>92871</v>
+        <v>79660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,21 +1991,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>568116</v>
+        <v>567992</v>
       </c>
       <c r="R14" t="n">
-        <v>6506669</v>
+        <v>6506757</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128912870</v>
+        <v>128912308</v>
       </c>
       <c r="B15" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567991</v>
+        <v>568116</v>
       </c>
       <c r="R15" t="n">
-        <v>6506744</v>
+        <v>6506669</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912730</v>
+        <v>128912870</v>
       </c>
       <c r="B16" t="n">
-        <v>79658</v>
+        <v>92873</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567992</v>
+        <v>567991</v>
       </c>
       <c r="R16" t="n">
-        <v>6506757</v>
+        <v>6506744</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,7 +2316,7 @@
         <v>128912804</v>
       </c>
       <c r="B17" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2427,7 +2427,7 @@
         <v>128912556</v>
       </c>
       <c r="B18" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>128912437</v>
       </c>
       <c r="B19" t="n">
-        <v>92175</v>
+        <v>92177</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
         <v>128912854</v>
       </c>
       <c r="B20" t="n">
-        <v>91960</v>
+        <v>91962</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>128912171</v>
       </c>
       <c r="B21" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>129044110</v>
       </c>
       <c r="B23" t="n">
-        <v>92175</v>
+        <v>92177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>129044023</v>
       </c>
       <c r="B24" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>129043539</v>
       </c>
       <c r="B25" t="n">
-        <v>92175</v>
+        <v>92177</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>129043245</v>
       </c>
       <c r="B26" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128912730</v>
+        <v>128912308</v>
       </c>
       <c r="B14" t="n">
-        <v>79660</v>
+        <v>92873</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,21 +1991,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567992</v>
+        <v>568116</v>
       </c>
       <c r="R14" t="n">
-        <v>6506757</v>
+        <v>6506669</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,14 +2084,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128912308</v>
+        <v>128912870</v>
       </c>
       <c r="B15" t="n">
         <v>92873</v>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568116</v>
+        <v>567991</v>
       </c>
       <c r="R15" t="n">
-        <v>6506669</v>
+        <v>6506744</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912870</v>
+        <v>128912730</v>
       </c>
       <c r="B16" t="n">
-        <v>92873</v>
+        <v>79660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567991</v>
+        <v>567992</v>
       </c>
       <c r="R16" t="n">
-        <v>6506744</v>
+        <v>6506757</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128856597</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128852128</v>
       </c>
       <c r="B3" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128848051</v>
       </c>
       <c r="B4" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128847827</v>
       </c>
       <c r="B6" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128847563</v>
       </c>
       <c r="B7" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128885129</v>
       </c>
       <c r="B8" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>128885108</v>
       </c>
       <c r="B9" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128884959</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>128885003</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128912582</v>
       </c>
       <c r="B12" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>128912308</v>
       </c>
       <c r="B14" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>128912870</v>
       </c>
       <c r="B15" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>128912556</v>
       </c>
       <c r="B18" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>128912437</v>
       </c>
       <c r="B19" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>128912854</v>
       </c>
       <c r="B20" t="n">
-        <v>91962</v>
+        <v>91971</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>129044110</v>
       </c>
       <c r="B23" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>129044023</v>
       </c>
       <c r="B24" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>129043539</v>
       </c>
       <c r="B25" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>129043245</v>
       </c>
       <c r="B26" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128856597</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128852128</v>
       </c>
       <c r="B3" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128848051</v>
       </c>
       <c r="B4" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128847827</v>
       </c>
       <c r="B6" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128847563</v>
       </c>
       <c r="B7" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128885129</v>
       </c>
       <c r="B8" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>128885108</v>
       </c>
       <c r="B9" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128884959</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>128885003</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1983,7 +1983,7 @@
         <v>128912308</v>
       </c>
       <c r="B14" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>128912870</v>
       </c>
       <c r="B15" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2424,32 +2424,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128912556</v>
+        <v>128912437</v>
       </c>
       <c r="B18" t="n">
-        <v>92859</v>
+        <v>92193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,13 +2462,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568009</v>
+        <v>568125</v>
       </c>
       <c r="R18" t="n">
-        <v>6506870</v>
+        <v>6506664</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2535,32 +2535,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128912437</v>
+        <v>128912556</v>
       </c>
       <c r="B19" t="n">
-        <v>92192</v>
+        <v>92860</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568125</v>
+        <v>568009</v>
       </c>
       <c r="R19" t="n">
-        <v>6506664</v>
+        <v>6506870</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
         <v>128912854</v>
       </c>
       <c r="B20" t="n">
-        <v>91971</v>
+        <v>91972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>129044110</v>
       </c>
       <c r="B23" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>129044023</v>
       </c>
       <c r="B24" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>129043539</v>
       </c>
       <c r="B25" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>129043245</v>
       </c>
       <c r="B26" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128856597</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128885129</v>
       </c>
       <c r="B8" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>128885108</v>
       </c>
       <c r="B9" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128884959</v>
       </c>
       <c r="B10" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>128885003</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128912308</v>
+        <v>128912730</v>
       </c>
       <c r="B14" t="n">
-        <v>92860</v>
+        <v>79660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,21 +1991,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>568116</v>
+        <v>567992</v>
       </c>
       <c r="R14" t="n">
-        <v>6506669</v>
+        <v>6506757</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,7 +2091,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128912870</v>
+        <v>128912308</v>
       </c>
       <c r="B15" t="n">
         <v>92860</v>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567991</v>
+        <v>568116</v>
       </c>
       <c r="R15" t="n">
-        <v>6506744</v>
+        <v>6506669</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912730</v>
+        <v>128912870</v>
       </c>
       <c r="B16" t="n">
-        <v>79660</v>
+        <v>92860</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567992</v>
+        <v>567991</v>
       </c>
       <c r="R16" t="n">
-        <v>6506757</v>
+        <v>6506744</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2424,32 +2424,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128912437</v>
+        <v>128912556</v>
       </c>
       <c r="B18" t="n">
-        <v>92193</v>
+        <v>92860</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,13 +2462,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568125</v>
+        <v>568009</v>
       </c>
       <c r="R18" t="n">
-        <v>6506664</v>
+        <v>6506870</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2535,32 +2535,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128912556</v>
+        <v>128912437</v>
       </c>
       <c r="B19" t="n">
-        <v>92860</v>
+        <v>92193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568009</v>
+        <v>568125</v>
       </c>
       <c r="R19" t="n">
-        <v>6506870</v>
+        <v>6506664</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128856597</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128852128</v>
       </c>
       <c r="B3" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128848051</v>
       </c>
       <c r="B4" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128847827</v>
       </c>
       <c r="B6" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128847563</v>
       </c>
       <c r="B7" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128885129</v>
       </c>
       <c r="B8" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>128885108</v>
       </c>
       <c r="B9" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128884959</v>
       </c>
       <c r="B10" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>128885003</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128912582</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128912730</v>
+        <v>128912308</v>
       </c>
       <c r="B14" t="n">
-        <v>79660</v>
+        <v>92863</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,21 +1991,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567992</v>
+        <v>568116</v>
       </c>
       <c r="R14" t="n">
-        <v>6506757</v>
+        <v>6506669</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128912308</v>
+        <v>128912730</v>
       </c>
       <c r="B15" t="n">
-        <v>92860</v>
+        <v>79662</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568116</v>
+        <v>567992</v>
       </c>
       <c r="R15" t="n">
-        <v>6506669</v>
+        <v>6506757</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,7 +2205,7 @@
         <v>128912870</v>
       </c>
       <c r="B16" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>128912804</v>
       </c>
       <c r="B17" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>128912556</v>
       </c>
       <c r="B18" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>128912437</v>
       </c>
       <c r="B19" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>128912854</v>
       </c>
       <c r="B20" t="n">
-        <v>91972</v>
+        <v>91975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>128912171</v>
       </c>
       <c r="B21" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>129044110</v>
       </c>
       <c r="B23" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>129044023</v>
       </c>
       <c r="B24" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>129043539</v>
       </c>
       <c r="B25" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>129043245</v>
       </c>
       <c r="B26" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -1980,7 +1980,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128912308</v>
+        <v>128912870</v>
       </c>
       <c r="B14" t="n">
         <v>92863</v>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>568116</v>
+        <v>567991</v>
       </c>
       <c r="R14" t="n">
-        <v>6506669</v>
+        <v>6506744</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128912730</v>
+        <v>128912308</v>
       </c>
       <c r="B15" t="n">
-        <v>79662</v>
+        <v>92863</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567992</v>
+        <v>568116</v>
       </c>
       <c r="R15" t="n">
-        <v>6506757</v>
+        <v>6506669</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,17 +2195,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912870</v>
+        <v>128912730</v>
       </c>
       <c r="B16" t="n">
-        <v>92863</v>
+        <v>79662</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567991</v>
+        <v>567992</v>
       </c>
       <c r="R16" t="n">
-        <v>6506744</v>
+        <v>6506757</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -1388,7 +1388,7 @@
         <v>128885108</v>
       </c>
       <c r="B9" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>128884959</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>128885003</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128912582</v>
       </c>
       <c r="B12" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,17 +1973,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128912870</v>
+        <v>128912730</v>
       </c>
       <c r="B14" t="n">
-        <v>92863</v>
+        <v>79663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,21 +1991,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567991</v>
+        <v>567992</v>
       </c>
       <c r="R14" t="n">
-        <v>6506744</v>
+        <v>6506757</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,7 +2094,7 @@
         <v>128912308</v>
       </c>
       <c r="B15" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,17 +2195,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912730</v>
+        <v>128912870</v>
       </c>
       <c r="B16" t="n">
-        <v>79662</v>
+        <v>92865</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567992</v>
+        <v>567991</v>
       </c>
       <c r="R16" t="n">
-        <v>6506757</v>
+        <v>6506744</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2316,7 +2316,7 @@
         <v>128912804</v>
       </c>
       <c r="B17" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>128912556</v>
       </c>
       <c r="B18" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>128912437</v>
       </c>
       <c r="B19" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>128912854</v>
       </c>
       <c r="B20" t="n">
-        <v>91975</v>
+        <v>91977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>128912171</v>
       </c>
       <c r="B21" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
         <v>129044110</v>
       </c>
       <c r="B23" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>129044023</v>
       </c>
       <c r="B24" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>129043539</v>
       </c>
       <c r="B25" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>129043245</v>
       </c>
       <c r="B26" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -1755,7 +1755,7 @@
         <v>128912582</v>
       </c>
       <c r="B12" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,17 +1973,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128912730</v>
+        <v>128912308</v>
       </c>
       <c r="B14" t="n">
-        <v>79663</v>
+        <v>92869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,21 +1991,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567992</v>
+        <v>568116</v>
       </c>
       <c r="R14" t="n">
-        <v>6506757</v>
+        <v>6506669</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,10 +2091,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128912308</v>
+        <v>128912870</v>
       </c>
       <c r="B15" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568116</v>
+        <v>567991</v>
       </c>
       <c r="R15" t="n">
-        <v>6506669</v>
+        <v>6506744</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912870</v>
+        <v>128912730</v>
       </c>
       <c r="B16" t="n">
-        <v>92865</v>
+        <v>79663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567991</v>
+        <v>567992</v>
       </c>
       <c r="R16" t="n">
-        <v>6506744</v>
+        <v>6506757</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2427,7 +2427,7 @@
         <v>128912556</v>
       </c>
       <c r="B18" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>128912437</v>
       </c>
       <c r="B19" t="n">
-        <v>92198</v>
+        <v>92202</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>128912854</v>
       </c>
       <c r="B20" t="n">
-        <v>91977</v>
+        <v>91981</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Eva Siljeholm, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2988,7 +2988,7 @@
         <v>129044110</v>
       </c>
       <c r="B23" t="n">
-        <v>92198</v>
+        <v>92202</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>129044023</v>
       </c>
       <c r="B24" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>129043539</v>
       </c>
       <c r="B25" t="n">
-        <v>92198</v>
+        <v>92202</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>129043245</v>
       </c>
       <c r="B26" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -2988,7 +2988,7 @@
         <v>129044110</v>
       </c>
       <c r="B23" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>129044023</v>
       </c>
       <c r="B24" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>129043539</v>
       </c>
       <c r="B25" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>129043245</v>
       </c>
       <c r="B26" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -2988,7 +2988,7 @@
         <v>129044110</v>
       </c>
       <c r="B23" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>129044023</v>
       </c>
       <c r="B24" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>129043539</v>
       </c>
       <c r="B25" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>129043245</v>
       </c>
       <c r="B26" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3427,6 +3427,136 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129866825</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Råsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>568020</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6506752</v>
+      </c>
+      <c r="S27" t="n">
+        <v>54</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>E-Nor-0869</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Sammanslaget av 4 rapporter</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3432,7 +3432,7 @@
         <v>129866825</v>
       </c>
       <c r="B27" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3432,7 +3432,7 @@
         <v>129866825</v>
       </c>
       <c r="B27" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3432,7 +3432,7 @@
         <v>129866825</v>
       </c>
       <c r="B27" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3432,7 +3432,7 @@
         <v>129866825</v>
       </c>
       <c r="B27" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3432,7 +3432,7 @@
         <v>129866825</v>
       </c>
       <c r="B27" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3432,7 +3432,7 @@
         <v>129866825</v>
       </c>
       <c r="B27" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3432,7 +3432,7 @@
         <v>129866825</v>
       </c>
       <c r="B27" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3562,7 +3562,7 @@
         <v>131180038</v>
       </c>
       <c r="B28" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3562,7 +3562,7 @@
         <v>131180038</v>
       </c>
       <c r="B28" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3562,7 +3562,7 @@
         <v>131180038</v>
       </c>
       <c r="B28" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>131237131</v>
       </c>
       <c r="B29" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>131237070</v>
       </c>
       <c r="B30" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3562,7 +3562,7 @@
         <v>131180038</v>
       </c>
       <c r="B28" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>131237131</v>
       </c>
       <c r="B29" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>131237070</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3562,7 +3562,7 @@
         <v>131180038</v>
       </c>
       <c r="B28" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>131237131</v>
       </c>
       <c r="B29" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>131237070</v>
       </c>
       <c r="B30" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3864,6 +3864,111 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131762229</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Udden i Råsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>568015</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6506936</v>
+      </c>
+      <c r="S31" t="n">
+        <v>50</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3659,7 +3659,7 @@
         <v>131237131</v>
       </c>
       <c r="B29" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>131237070</v>
       </c>
       <c r="B30" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3659,7 +3659,7 @@
         <v>131237131</v>
       </c>
       <c r="B29" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>131237070</v>
       </c>
       <c r="B30" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>131762229</v>
       </c>
       <c r="B31" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3869,7 +3869,7 @@
         <v>131762229</v>
       </c>
       <c r="B31" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3869,7 +3869,7 @@
         <v>131762229</v>
       </c>
       <c r="B31" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3869,7 +3869,7 @@
         <v>131762229</v>
       </c>
       <c r="B31" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3969,6 +3969,144 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132553309</v>
+      </c>
+      <c r="B32" t="n">
+        <v>56890</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Udden glotternskogen, Ög</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>568005</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6506900</v>
+      </c>
+      <c r="S32" t="n">
+        <v>50</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2 individer som simmade in till motsatt strand.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kråka Larsen</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kråka Larsen</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3974,7 +3974,7 @@
         <v>132553309</v>
       </c>
       <c r="B32" t="n">
-        <v>56890</v>
+        <v>56891</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3974,7 +3974,7 @@
         <v>132553309</v>
       </c>
       <c r="B32" t="n">
-        <v>56891</v>
+        <v>56895</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -3974,7 +3974,7 @@
         <v>132553309</v>
       </c>
       <c r="B32" t="n">
-        <v>56895</v>
+        <v>56898</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -675,57 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128856597</v>
+        <v>128912171</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råsjön, Råsjön, Ög</t>
+          <t>Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568029</v>
+        <v>568118</v>
       </c>
       <c r="R2" t="n">
-        <v>6506740</v>
+        <v>6506590</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,74 +746,88 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128852128</v>
+        <v>128912582</v>
       </c>
       <c r="B3" t="n">
-        <v>92196</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Råsjön, Råsjön, Ög</t>
+          <t>Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568039</v>
+        <v>568004</v>
       </c>
       <c r="R3" t="n">
-        <v>6506731</v>
+        <v>6506793</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,39 +857,50 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128848051</v>
+        <v>131180038</v>
       </c>
       <c r="B4" t="n">
-        <v>91564</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,37 +908,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Råsjöbäcken, Råsjöbäcken, Ög</t>
+          <t>Råsjön, Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568107</v>
+        <v>568061</v>
       </c>
       <c r="R4" t="n">
-        <v>6506669</v>
+        <v>6506679</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -943,12 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128847282</v>
+        <v>128912854</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>92348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,34 +1005,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Råsjöbäcken, Råsjöbäcken, Ög</t>
+          <t>Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568135</v>
+        <v>567998</v>
       </c>
       <c r="R5" t="n">
-        <v>6506592</v>
+        <v>6506728</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1043,61 +1065,72 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128847827</v>
+        <v>128848051</v>
       </c>
       <c r="B6" t="n">
-        <v>92196</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,13 +1140,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568105</v>
+        <v>568107</v>
       </c>
       <c r="R6" t="n">
-        <v>6506631</v>
+        <v>6506669</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1172,7 +1205,7 @@
         <v>128847563</v>
       </c>
       <c r="B7" t="n">
-        <v>92863</v>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,64 +1299,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128885129</v>
+        <v>128912308</v>
       </c>
       <c r="B8" t="n">
-        <v>105774</v>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mossen NO 1390 m, Ög</t>
+          <t>Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568037</v>
+        <v>568116</v>
       </c>
       <c r="R8" t="n">
-        <v>6506715</v>
+        <v>6506669</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,9 +1370,19 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1365,84 +1395,66 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128885108</v>
+        <v>128912556</v>
       </c>
       <c r="B9" t="n">
-        <v>98712</v>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mossen NO 1390 m, Ög</t>
+          <t>Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568037</v>
+        <v>568009</v>
       </c>
       <c r="R9" t="n">
-        <v>6506715</v>
+        <v>6506870</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1469,9 +1481,19 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1484,84 +1506,66 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128884959</v>
+        <v>128912870</v>
       </c>
       <c r="B10" t="n">
-        <v>98712</v>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mossen NO 1420 m, Ög</t>
+          <t>Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568015</v>
+        <v>567991</v>
       </c>
       <c r="R10" t="n">
-        <v>6506779</v>
+        <v>6506744</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1588,14 +1592,19 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>I närområdet är totalt 149 knärotsskott observerade.</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,81 +1617,63 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128885003</v>
+        <v>129043245</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>93235</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mossen NO 1440 m, Ög</t>
+          <t>Nära parkeringsplats vid Råsjön, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568021</v>
+        <v>568162</v>
       </c>
       <c r="R11" t="n">
-        <v>6506793</v>
+        <v>6506596</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,17 +1700,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>I närområdet är totalt 149 knärotsskott observerade.</t>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1732,30 +1728,25 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Hasse Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Hasse Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128912582</v>
+        <v>129044023</v>
       </c>
       <c r="B12" t="n">
-        <v>91549</v>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,21 +1754,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1786,17 +1777,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Råsjön, Ög</t>
+          <t>Grillplatsen på udden, Råsjön, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568004</v>
+        <v>567995</v>
       </c>
       <c r="R12" t="n">
-        <v>6506793</v>
+        <v>6506914</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1820,22 +1811,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,22 +1842,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Hasse Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Hasse Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128920148</v>
+        <v>128847827</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>92567</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,46 +1865,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Råsjön, Ög</t>
+          <t>Råsjöbäcken, Råsjöbäcken, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568107</v>
+        <v>568105</v>
       </c>
       <c r="R13" t="n">
-        <v>6506598</v>
+        <v>6506631</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1940,91 +1922,77 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128912308</v>
+        <v>128852128</v>
       </c>
       <c r="B14" t="n">
-        <v>92869</v>
+        <v>92567</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Råsjön, Ög</t>
+          <t>Råsjön, Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>568116</v>
+        <v>568039</v>
       </c>
       <c r="R14" t="n">
-        <v>6506669</v>
+        <v>6506731</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2051,72 +2019,61 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128912870</v>
+        <v>128912437</v>
       </c>
       <c r="B15" t="n">
-        <v>92869</v>
+        <v>92567</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>6031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567991</v>
+        <v>568125</v>
       </c>
       <c r="R15" t="n">
-        <v>6506744</v>
+        <v>6506664</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2121,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2174,7 +2131,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,32 +2159,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128912730</v>
+        <v>129043539</v>
       </c>
       <c r="B16" t="n">
-        <v>79663</v>
+        <v>92567</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2236,17 +2193,17 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Råsjön, Ög</t>
+          <t>Udde ut i Råsjön, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567992</v>
+        <v>568034</v>
       </c>
       <c r="R16" t="n">
-        <v>6506757</v>
+        <v>6506778</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2270,22 +2227,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2301,44 +2258,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Hasse Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Hasse Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128912804</v>
+        <v>129044110</v>
       </c>
       <c r="B17" t="n">
-        <v>79663</v>
+        <v>92567</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2347,17 +2304,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Råsjön, Ög</t>
+          <t>Yttersta området på udden, Råsjön, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567994</v>
+        <v>568021</v>
       </c>
       <c r="R17" t="n">
-        <v>6506732</v>
+        <v>6506917</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2381,22 +2338,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,22 +2369,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Hasse Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Hasse Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128912556</v>
+        <v>128912730</v>
       </c>
       <c r="B18" t="n">
-        <v>92869</v>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2435,21 +2392,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,13 +2419,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568009</v>
+        <v>567992</v>
       </c>
       <c r="R18" t="n">
-        <v>6506870</v>
+        <v>6506757</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2535,32 +2492,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128912437</v>
+        <v>128912804</v>
       </c>
       <c r="B19" t="n">
-        <v>92202</v>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6031</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2573,10 +2530,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568125</v>
+        <v>567994</v>
       </c>
       <c r="R19" t="n">
-        <v>6506664</v>
+        <v>6506732</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,7 +2565,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2618,7 +2575,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2646,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128912854</v>
+        <v>131237070</v>
       </c>
       <c r="B20" t="n">
-        <v>91981</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2657,37 +2614,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Råsjön, Ög</t>
+          <t>Udden i Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567998</v>
+        <v>568119</v>
       </c>
       <c r="R20" t="n">
-        <v>6506728</v>
+        <v>6506603</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,22 +2676,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2738,70 +2690,74 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128912171</v>
+        <v>131237131</v>
       </c>
       <c r="B21" t="n">
-        <v>78710</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Råsjön, Ög</t>
+          <t>Udden i Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568118</v>
+        <v>568107</v>
       </c>
       <c r="R21" t="n">
-        <v>6506590</v>
+        <v>6506605</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2825,22 +2781,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2849,29 +2795,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128920214</v>
+        <v>131762229</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>57972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2879,46 +2824,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Råsjön, Ög</t>
+          <t>Udden i Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>568014</v>
+        <v>568015</v>
       </c>
       <c r="R22" t="n">
-        <v>6506845</v>
+        <v>6506936</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2942,22 +2886,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2966,29 +2900,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129044110</v>
+        <v>132553309</v>
       </c>
       <c r="B23" t="n">
-        <v>92206</v>
+        <v>56915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2996,40 +2929,62 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6031</v>
+        <v>100088</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Yttersta området på udden, Råsjön, Nedre Glottern, Ög</t>
+          <t>Udden glotternskogen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>568021</v>
+        <v>568005</v>
       </c>
       <c r="R23" t="n">
-        <v>6506917</v>
+        <v>6506900</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3053,22 +3008,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2 individer som simmade in till motsatt strand.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3084,63 +3044,69 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Kråka Larsen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Kråka Larsen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129044023</v>
+        <v>128920214</v>
       </c>
       <c r="B24" t="n">
-        <v>92873</v>
+        <v>5179</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grillplatsen på udden, Råsjön, Nedre Glottern, Ög</t>
+          <t>Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567995</v>
+        <v>568014</v>
       </c>
       <c r="R24" t="n">
-        <v>6506914</v>
+        <v>6506845</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3164,22 +3130,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3195,22 +3161,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129043539</v>
+        <v>128847282</v>
       </c>
       <c r="B25" t="n">
-        <v>92206</v>
+        <v>8455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3218,40 +3184,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6031</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Udde ut i Råsjön, Nedre Glottern, Ög</t>
+          <t>Råsjöbäcken, Råsjöbäcken, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568034</v>
+        <v>568135</v>
       </c>
       <c r="R25" t="n">
-        <v>6506778</v>
+        <v>6506592</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3275,22 +3238,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:53</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:53</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3299,67 +3252,72 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129043245</v>
+        <v>128920148</v>
       </c>
       <c r="B26" t="n">
-        <v>92873</v>
+        <v>8455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nära parkeringsplats vid Råsjön, Nedre Glottern, Ög</t>
+          <t>Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568162</v>
+        <v>568107</v>
       </c>
       <c r="R26" t="n">
-        <v>6506596</v>
+        <v>6506598</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3386,22 +3344,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3417,22 +3375,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Lena Lundin Johansson, Eva Siljeholm, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129866825</v>
+        <v>128856597</v>
       </c>
       <c r="B27" t="n">
-        <v>98833</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3459,32 +3417,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Råsjön, Ög</t>
+          <t>Råsjön, Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>568020</v>
+        <v>568029</v>
       </c>
       <c r="R27" t="n">
-        <v>6506752</v>
+        <v>6506740</v>
       </c>
       <c r="S27" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3506,11 +3459,6 @@
           <t>Kvillinge</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>E-Nor-0869</t>
-        </is>
-      </c>
       <c r="Y27" t="inlineStr">
         <is>
           <t>2025-10-02</t>
@@ -3521,11 +3469,6 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Sammanslaget av 4 rapporter</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3534,73 +3477,80 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Karin Nyström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131180038</v>
+        <v>128884959</v>
       </c>
       <c r="B28" t="n">
-        <v>91828</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Råsjön, Råsjön, Ög</t>
+          <t>Mossen NO 1420 m, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>568061</v>
+        <v>568015</v>
       </c>
       <c r="R28" t="n">
-        <v>6506679</v>
+        <v>6506779</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3624,12 +3574,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>I närområdet är totalt 149 knärotsskott observerade.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3638,71 +3593,85 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131237131</v>
+        <v>128885003</v>
       </c>
       <c r="B29" t="n">
-        <v>57899</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Udden i Råsjön, Ög</t>
+          <t>Mossen NO 1440 m, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>568107</v>
+        <v>568021</v>
       </c>
       <c r="R29" t="n">
-        <v>6506605</v>
+        <v>6506793</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3729,12 +3698,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>I närområdet är totalt 149 knärotsskott observerade.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3743,71 +3717,85 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131237070</v>
+        <v>128885108</v>
       </c>
       <c r="B30" t="n">
-        <v>57899</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Udden i Råsjön, Ög</t>
+          <t>Mossen NO 1390 m, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>568119</v>
+        <v>568037</v>
       </c>
       <c r="R30" t="n">
-        <v>6506603</v>
+        <v>6506715</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3834,12 +3822,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3848,74 +3836,86 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131762229</v>
+        <v>129866825</v>
       </c>
       <c r="B31" t="n">
-        <v>57945</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Udden i Råsjön, Ög</t>
+          <t>Råsjön, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>568015</v>
+        <v>568020</v>
       </c>
       <c r="R31" t="n">
-        <v>6506936</v>
+        <v>6506752</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3937,14 +3937,24 @@
           <t>Kvillinge</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>E-Nor-0869</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Sammanslaget av 4 rapporter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3955,26 +3965,35 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Karin Nyström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132553309</v>
+        <v>128885129</v>
       </c>
       <c r="B32" t="n">
-        <v>56898</v>
+        <v>106243</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3982,62 +4001,53 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100088</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Udden glotternskogen, Ög</t>
+          <t>Mossen NO 1390 m, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>568005</v>
+        <v>568037</v>
       </c>
       <c r="R32" t="n">
-        <v>6506900</v>
+        <v>6506715</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4061,27 +4071,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2 individer som simmade in till motsatt strand.</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4094,15 +4089,20 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kråka Larsen</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kråka Larsen</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 45488-2025 artfynd.xlsx
+++ b/artfynd/A 45488-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912171</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912582</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131180038</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912854</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848051</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128847563</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912308</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912556</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,6 +1674,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912870</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1740,6 +1790,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129043245</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1851,6 +1906,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129044023</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1948,6 +2008,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128847827</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2045,6 +2110,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128852128</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,6 +2226,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912437</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2267,6 +2342,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129043539</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2378,6 +2458,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129044110</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2489,6 +2574,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912730</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2600,6 +2690,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128912804</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131237070</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2810,6 +2910,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131237131</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2915,6 +3020,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131762229</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3053,6 +3163,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132553309</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3170,6 +3285,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920214</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3267,6 +3387,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128847282</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3384,6 +3509,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128920148</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3490,6 +3620,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128856597</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3614,6 +3749,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128884959</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3738,6 +3878,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128885003</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3857,6 +4002,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128885108</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3987,6 +4137,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129866825</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4106,8 +4261,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128885129</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>